--- a/4FINGERS_POC_Spec_and_Build_Tracker.xlsx
+++ b/4FINGERS_POC_Spec_and_Build_Tracker.xlsx
@@ -10537,7 +10537,7 @@
       </c>
       <c r="H19" s="57" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="I19" s="57" t="inlineStr">
@@ -10547,7 +10547,7 @@
       </c>
       <c r="J19" s="57" t="inlineStr">
         <is>
-          <t>Partial</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K19" s="57" t="str"/>
@@ -10606,7 +10606,7 @@
       </c>
       <c r="H20" s="57" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Blocked</t>
         </is>
       </c>
       <c r="I20" s="57" t="inlineStr">
@@ -10616,10 +10616,14 @@
       </c>
       <c r="J20" s="57" t="inlineStr">
         <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="K20" s="57" t="str"/>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="K20" s="57" t="inlineStr">
+        <is>
+          <t>Deploy requires the user's own Vercel account + real ANTHROPIC_API_KEY (not available in the build environment). App is deploy-ready; see README.md Deployment section.</t>
+        </is>
+      </c>
       <c r="L20" s="57" t="str"/>
       <c r="M20" s="57" t="inlineStr">
         <is>
@@ -10675,7 +10679,7 @@
       </c>
       <c r="H21" s="57" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="I21" s="57" t="inlineStr">
@@ -10685,7 +10689,7 @@
       </c>
       <c r="J21" s="57" t="inlineStr">
         <is>
-          <t>Not Run</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K21" s="57" t="str"/>
